--- a/public/inputs/y06-science - input.xlsx
+++ b/public/inputs/y06-science - input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.1 Predict</t>
+          <t>1.1 The circulatory system</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.2 Observe</t>
+          <t>1.2 The respiratory system</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3 Results</t>
+          <t>1.3 The reproductive system</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4 Reflect</t>
+          <t>1.4 Diseases</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.1 Predict</t>
+          <t>2.1 Properties of substances</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.2 Observe</t>
+          <t>2.2 Thermal and electrical conductors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -545,7 +545,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.3 Results</t>
+          <t>2.3 Reversible changes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.4 Reflect</t>
+          <t>2.4 Chemical reactions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.1 Predict</t>
+          <t>3.1 Igneous rocks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.2 Observe</t>
+          <t>3.2 Sedimentary rocks and fossils</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.3 Results</t>
+          <t>3.3 Metamorphic rocks and the rock cycle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.4 Reflect</t>
+          <t>3.4 Soil</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.1 Predict</t>
+          <t>4.1 Food chains, food webs and energy transfers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.2 Observe</t>
+          <t>4.2 harm to food chains and food webs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -670,12 +670,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.3 Results</t>
+          <t>Unit 5 · Forces and electricity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.4 Reflect</t>
+          <t>5.1 Mass and weight</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -696,12 +696,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unit 5 · Forces and electricity</t>
+          <t>5.2 The effects of forces</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.1 Predict</t>
+          <t>5.3 Floating and sinking</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5.2 Observe</t>
+          <t>5.4 Different circuits and circuit diagrams</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -735,12 +735,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5.3 Results</t>
+          <t>Unit 6 · Light and the solar system</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.4 Reflect</t>
+          <t>6.1 Reflection</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -761,12 +761,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Unit 6 · Light and the solar system</t>
+          <t>6.2 Refraction</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6.1 Predict</t>
+          <t>6.3 The solar system</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -787,12 +787,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6.2 Observe</t>
+          <t>Term 1 Revision</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -800,12 +800,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.3 Results</t>
+          <t>Term 1 Assessment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -813,15 +813,223 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.4 Reflect</t>
+          <t>Term 1 Animal Theory</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Term 1 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Term 1 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Term 1 School Activities</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Term 2 Revision</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Term 2 Assessment</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Term 2 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Term 2 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Term 2 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Term 2 School Activities</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Term 3 Revision</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Term 3 Assessment</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Term 3 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Term 3 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Term 3 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Term 3 School Activities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Animal Theory</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
